--- a/branches/pt/CodeSystem-pt-route-cs.xlsx
+++ b/branches/pt/CodeSystem-pt-route-cs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://www.infarmed.pt/routes</t>
+    <t>http://medigree.net/fhir/mpd5/CodeSystem/pt-route-cs</t>
   </si>
   <si>
     <t>Version</t>
@@ -36,13 +36,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>PTROUTECS</t>
+    <t>PTRouteCS</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>Lymph node code system</t>
+    <t>Route of administration code system</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-24T21:33:25+00:00</t>
+    <t>2022-08-29T19:31:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Lymph node terms that could not be found in standard sources such as SNOMED CT.</t>
+    <t>Route of administration code system.</t>
   </si>
   <si>
     <t>Purpose</t>
